--- a/CQ_EvalSummary.xlsx
+++ b/CQ_EvalSummary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meggo/Dropbox/Housing Potential Shared Folder/HICC Ontology Report/Phase 3/HICC Report Distribution Dec 12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9082C38-0105-984D-A72E-478D0B0E4DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC70766C-98D2-C04C-89B0-F301119CC74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="900" windowWidth="29920" windowHeight="16860" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1851,7 +1851,39 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT ?nearbyuse {
+    <t>SELECT ?nearbyuse WHERE {{
+    &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#Building3efdd236cedae97c4e70c81227035d4a&gt; loc:hasLocation [geo:asWKT ?pwkt].
+    ?s a hp:Building;
+    hp:occupies [loc:hasLocation [geo:asWKT ?nearbywkt]];
+    bdg:use ?nearbyuse.
+    FILTER ((?nearbyuse != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#BuildingUseHouse&gt;) || (?nearbyuse != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#BuildingUseHighRiseApartment&gt;) || (?nearbyuse != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#BuildingUseLowRiseApartment&gt;))
+    FILTER(geof:distance(?pwkt, ?nearbywkt, uom:metre) &lt; 400) #within 400m
+}
+    UNION
+    { 
+    &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#Building3efdd236cedae97c4e70c81227035d4a&gt; loc:hasLocation [geo:asWKT ?pwkt].
+    ?source hp:definesRegulation ?reg.
+   ?source a hp:ZoningBylaw.
+?reg a hp:Regulation;
+    hp:definedFor [loc:hasLocation [geo:asWKT ?regwkt]];
+    hp:designatesZoningType [oz:allowsUse ?nearbyuse].
+	FILTER(geof:distance(?pwkt, ?regwkt, uom:metre) &lt; 400) #within 400m
+    FILTER ((?nearbyuse != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#Residential&gt;)||(?use != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#Residential&gt;)) #all uses except residential might constitute employment opportunities
+    #alternatively, could filter specifically for e.g. office or industrial type use
+}	
+        }</t>
+  </si>
+  <si>
+    <t>SELECT ?nearbyuse WHERE {{
+    &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#Building3efdd236cedae97c4e70c81227035d4a&gt; loc:hasLocation [geo:asWKT ?pwkt].
+    ?s a hp:Building;
+    hp:occupies [loc:hasLocation [geo:asWKT ?nearbywkt]];
+    bdg:use ?nearbyuse.
+    FILTER ((?nearbyuse != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#BuildingUseHouse&gt;) || (?nearbyuse != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#BuildingUseHighRiseApartment&gt;) || (?nearbyuse != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#BuildingUseLowRiseApartment&gt;))
+    FILTER(geof:distance(?pwkt, ?nearbywkt, uom:metre) &lt; 400) #within 400m
+}
+    UNION
+    { 
     &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#Property5230346&gt; loc:hasLocation [geo:asWKT ?pwkt].
     #regulations
     ?source hp:definesRegulation ?reg.
@@ -1860,22 +1892,10 @@
     hp:definedFor [loc:hasLocation [geo:asWKT ?regwkt]];
     hp:designatesZoningType [oz:allowsUse ?nearbyuse].
 	FILTER(geof:distance(?pwkt, ?regwkt, uom:metre) &lt; 4000) #within 400m
-    FILTER ((?use != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#Residential&gt;)||(?use != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#Residential&gt;)) #all uses except residential might constitute employment opportunities
+    FILTER ((?nearbyuse != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#Residential&gt;)||(?use != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#Residential&gt;)) #all uses except residential might constitute employment opportunities
     #alternatively, could filter specifically for e.g. office or industrial type use
-}	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELECT ?nearbyuse {
-    &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#Building3efdd236cedae97c4e70c81227035d4a&gt; loc:hasLocation [geo:asWKT ?pwkt].
-    ?source hp:definesRegulation ?reg.
-   ?source a hp:ZoningBylaw.
-?reg a hp:Regulation;
-    hp:definedFor [loc:hasLocation [geo:asWKT ?regwkt]];
-    hp:designatesZoningType [oz:allowsUse ?nearbyuse].
-	FILTER(geof:distance(?pwkt, ?regwkt, uom:metre) &lt; 400) #within 400m
-    FILTER ((?use != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#Residential&gt;)||(?use != &lt;http://ontology.eil.utoronto.ca/Toronto/Toronto#Residential&gt;)) #all uses except residential might constitute employment opportunities
-    #alternatively, could filter specifically for e.g. office or industrial type use
-}	</t>
+        }
+}</t>
   </si>
 </sst>
 </file>
@@ -2175,7 +2195,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2270,19 +2290,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2998,7 +3005,7 @@
       <c r="C18" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="D18" s="43" t="s">
+      <c r="D18" s="27" t="s">
         <v>237</v>
       </c>
       <c r="E18" s="27"/>
@@ -3012,7 +3019,7 @@
         <v>235</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="43" t="s">
+      <c r="D19" s="27" t="s">
         <v>128</v>
       </c>
       <c r="E19" s="27"/>
@@ -3025,7 +3032,7 @@
         <v>234</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="27" t="s">
         <v>128</v>
       </c>
       <c r="E20" s="15"/>
@@ -3042,7 +3049,7 @@
       <c r="C21" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D21" s="42" t="s">
+      <c r="D21" s="4" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3053,7 +3060,7 @@
       <c r="C22" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="43"/>
+      <c r="D22" s="27"/>
     </row>
     <row r="23" spans="1:7" ht="238">
       <c r="A23" s="3" t="s">
@@ -3185,7 +3192,7 @@
       <c r="C30" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D30" s="42" t="s">
+      <c r="D30" s="4" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3235,7 +3242,7 @@
       <c r="A34" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="14" t="s">
         <v>230</v>
       </c>
       <c r="C34" s="14"/>
@@ -3598,7 +3605,7 @@
       <c r="D11" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="44"/>
+      <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
@@ -3797,7 +3804,7 @@
       <c r="A20" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="4" t="s">
         <v>239</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -4344,14 +4351,14 @@
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" spans="1:7" ht="224">
+    <row r="21" spans="1:7" ht="409.6">
       <c r="A21" s="32" t="s">
         <v>72</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="C21" s="45" t="s">
+        <v>242</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>128</v>
       </c>
       <c r="D21" s="7" t="s">
@@ -4360,14 +4367,14 @@
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
     </row>
-    <row r="22" spans="1:7" ht="224">
+    <row r="22" spans="1:7" ht="409.6">
       <c r="A22" s="3" t="s">
         <v>73</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C22" s="42" t="s">
+        <v>241</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>128</v>
       </c>
       <c r="D22" s="7" t="s">
